--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1109-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1109-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B28312FC-B445-471F-BFD6-9FC1721BCA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{67C90185-5043-4844-AF4E-E6EDE0CC949F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{6F06BB8E-2C3A-43CB-A05F-953D6B6A5A1E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{614D595F-DA82-47AE-8578-A9510D814E88}"/>
   </bookViews>
   <sheets>
     <sheet name="1109-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1604,29 +1604,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0841AE0-3E50-40A4-9D46-4F49206205A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{232A3F32-061D-4506-8AAD-037A2F2F053B}">
   <dimension ref="A1:X51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1660,7 +1659,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1696,7 +1695,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1748,7 +1747,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1816,7 +1815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1888,7 +1887,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1960,7 +1959,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2032,7 +2031,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2104,7 +2103,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2176,7 +2175,7 @@
         <v>8.33</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2248,7 +2247,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2320,7 +2319,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2392,7 +2391,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2464,7 +2463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2536,7 +2535,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2608,7 +2607,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2680,7 +2679,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2752,7 +2751,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2824,7 +2823,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2896,7 +2895,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2968,7 +2967,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -3040,7 +3039,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3112,7 +3111,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3184,7 +3183,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3256,7 +3255,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3328,7 +3327,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="41">
         <v>2003</v>
       </c>
@@ -3400,7 +3399,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="43"/>
       <c r="B27" s="44"/>
       <c r="C27" s="18" t="s">
@@ -3428,7 +3427,7 @@
       <c r="W27" s="50"/>
       <c r="X27" s="46"/>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2002</v>
       </c>
@@ -3500,7 +3499,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2001</v>
       </c>
@@ -3572,7 +3571,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2000</v>
       </c>
@@ -3644,7 +3643,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>1999</v>
       </c>
@@ -3716,7 +3715,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1998</v>
       </c>
@@ -3788,7 +3787,7 @@
         <v>5.93</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>1997</v>
       </c>
@@ -3860,7 +3859,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="43"/>
       <c r="B34" s="44"/>
       <c r="C34" s="18" t="s">
@@ -3888,7 +3887,7 @@
       <c r="W34" s="50"/>
       <c r="X34" s="46"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="51">
         <v>1996</v>
       </c>
@@ -3960,7 +3959,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="53"/>
       <c r="B36" s="54"/>
       <c r="C36" s="20" t="s">
@@ -3988,7 +3987,7 @@
       <c r="W36" s="60"/>
       <c r="X36" s="56"/>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>1995</v>
       </c>
@@ -4060,7 +4059,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="51">
         <v>1994</v>
       </c>
@@ -4132,7 +4131,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="53"/>
       <c r="B39" s="54"/>
       <c r="C39" s="20" t="s">
@@ -4160,7 +4159,7 @@
       <c r="W39" s="60"/>
       <c r="X39" s="56"/>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>1993</v>
       </c>
@@ -4232,7 +4231,7 @@
         <v>6.56</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="51">
         <v>1992</v>
       </c>
@@ -4304,7 +4303,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="53"/>
       <c r="B42" s="54"/>
       <c r="C42" s="20" t="s">
@@ -4332,7 +4331,7 @@
       <c r="W42" s="60"/>
       <c r="X42" s="56"/>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41">
         <v>1991</v>
       </c>
@@ -4404,7 +4403,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="43"/>
       <c r="B44" s="44"/>
       <c r="C44" s="18" t="s">
@@ -4432,7 +4431,7 @@
       <c r="W44" s="50"/>
       <c r="X44" s="46"/>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="51">
         <v>1990</v>
       </c>
@@ -4504,7 +4503,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="53"/>
       <c r="B46" s="54"/>
       <c r="C46" s="20" t="s">
@@ -4532,7 +4531,7 @@
       <c r="W46" s="60"/>
       <c r="X46" s="56"/>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>1989</v>
       </c>
@@ -4604,7 +4603,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37">
         <v>1987</v>
       </c>
@@ -4676,7 +4675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>1984</v>
       </c>
@@ -4748,7 +4747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>1983</v>
       </c>
@@ -4820,7 +4819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39" t="s">
         <v>70</v>
       </c>
